--- a/astro-site/public/dl/manual-chef-ejecutivo/ficha-tecnica-proceso.xlsx
+++ b/astro-site/public/dl/manual-chef-ejecutivo/ficha-tecnica-proceso.xlsx
@@ -2148,7 +2148,11 @@
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
-      <c r="F24" s="8" t="inlineStr"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Salpimentado uniforme y sin jugo en la bandeja: el solomillo pierde el frío de cámara al tacto.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="15" t="n">
@@ -2162,7 +2166,11 @@
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
-      <c r="F25" s="8" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>El puré pasa por el colador sin grumos y sale a 63 °C o más.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="15" t="n">
@@ -2176,7 +2184,11 @@
       <c r="C26" s="5" t="n"/>
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
-      <c r="F26" s="8" t="inlineStr"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Cebolla transparente y blanda, sin ningún punto dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="15" t="n">
@@ -2190,7 +2202,11 @@
       <c r="C27" s="5" t="n"/>
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
-      <c r="F27" s="8" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>La salsa napa el dorso de una cuchara y sale colada, sin grumos.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="15" t="n">
@@ -2204,7 +2220,11 @@
       <c r="C28" s="5" t="n"/>
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
-      <c r="F28" s="8" t="inlineStr"/>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Marca dorada uniforme en las dos caras, sin jugo en la plancha.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="15" t="n">
@@ -2218,7 +2238,11 @@
       <c r="C29" s="5" t="n"/>
       <c r="D29" s="5" t="n"/>
       <c r="E29" s="5" t="n"/>
-      <c r="F29" s="8" t="inlineStr"/>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Sonda al centro: 58 °C antes del reposo.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="15" t="n">
@@ -2232,7 +2256,11 @@
       <c r="C30" s="5" t="n"/>
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="n"/>
-      <c r="F30" s="8" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Panceta dorada y crujiente entre los dos papeles, sin quemarse en los bordes.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="15" t="n">
@@ -2246,7 +2274,11 @@
       <c r="C31" s="5" t="n"/>
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="n"/>
-      <c r="F31" s="8" t="inlineStr"/>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Peso de la ración y foto de referencia.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="15" t="n">
@@ -3776,7 +3808,7 @@
         </is>
       </c>
       <c r="F22" s="21" t="n">
-        <v>46287</v>
+        <v>46256</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -3790,7 +3822,7 @@
       </c>
       <c r="I22" s="22">
         <f>IFERROR(IF(OR($F22="",$C$5=""),"",$C$5-$F22),"")</f>
-        <v>-16.0</v>
+        <v>15.0</v>
       </c>
       <c r="J22" t="str">
         <f>IF($B22="","",IF($H22="",$A$45,IF($H22=$A$49,$A$43,IF(OR($I22="",$C$6=""),$A$42,IF($I22&gt;$C$6,$A$44,$A$42)))))</f>
@@ -3824,7 +3856,7 @@
         </is>
       </c>
       <c r="F23" s="21" t="n">
-        <v>46289</v>
+        <v>46258</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -3838,7 +3870,7 @@
       </c>
       <c r="I23" s="22">
         <f>IFERROR(IF(OR($F23="",$C$5=""),"",$C$5-$F23),"")</f>
-        <v>-18.0</v>
+        <v>13.0</v>
       </c>
       <c r="J23" t="str">
         <f>IF($B23="","",IF($H23="",$A$45,IF($H23=$A$49,$A$43,IF(OR($I23="",$C$6=""),$A$42,IF($I23&gt;$C$6,$A$44,$A$42)))))</f>
